--- a/evaluation/results_with_metrics.xlsx
+++ b/evaluation/results_with_metrics.xlsx
@@ -1047,20 +1047,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The arbitration proceedings will be conducted in Kanpur.</t>
+          <t>The arbitration proceedings will be conducted at Kanpur.</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.3189</v>
+        <v>0.3135</v>
       </c>
       <c r="E20" t="n">
-        <v>0.869</v>
+        <v>0.868</v>
       </c>
       <c r="F20" t="n">
-        <v>0.912</v>
+        <v>0.911</v>
       </c>
       <c r="G20" t="n">
-        <v>0.89</v>
+        <v>0.889</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1079,20 +1079,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The arbitrator, who is appointed by the Deputy Director of the Institute, conducts arbitration.</t>
+          <t>The arbitrator, who is appointed by the Deputy Director of the Institute, conducts the arbitration.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6401</v>
+        <v>0.6474</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8941</v>
+        <v>0.8948</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9084</v>
+        <v>0.9097</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9012</v>
+        <v>0.9022</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
